--- a/sample_data/school_calendar_sample.xlsx
+++ b/sample_data/school_calendar_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,103 +424,97 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Event Type</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Is School Day</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Display Text</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Colour</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Half-Term Break</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Half-Term Break</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Green</t>
+          <t>National Day</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Typhoon Closure</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Typhoon Closure</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Red</t>
+          <t>Mid-Autumn Festival</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Term Break</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Public Holiday</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Red</t>
+          <t>Mid-Term Break (test override)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Typhoon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T8 Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Closure</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Facility Maintenance</t>
         </is>
       </c>
     </row>
